--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3289,7 +3289,7 @@
         <v>17390</v>
       </c>
       <c r="K64" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65">
@@ -14044,7 +14044,7 @@
         <v>28635</v>
       </c>
       <c r="K64" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3286,10 +3286,10 @@
         <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17390</v>
+        <v>17421</v>
       </c>
       <c r="K64" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
@@ -14017,13 +14017,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>260842</v>
+        <v>263111</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.0007355363669100577</v>
+        <v>0.007956817885792656</v>
       </c>
       <c r="E64" t="n">
         <v>5</v>
@@ -14060,7 +14060,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.07751052361199499</v>
+        <v>-0.08546583001090795</v>
       </c>
       <c r="E65" t="n">
         <v>6</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3286,10 +3286,10 @@
         <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17421</v>
+        <v>17469</v>
       </c>
       <c r="K64" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65">
@@ -6874,7 +6874,7 @@
         <v>18497</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3271,7 +3271,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>50052</v>
@@ -3286,10 +3286,10 @@
         <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17469</v>
+        <v>17483</v>
       </c>
       <c r="K64" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -6856,7 +6856,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>196403</v>
@@ -10441,7 +10441,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>36403</v>
@@ -14026,7 +14026,7 @@
         <v>0.007956817885792656</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>231867</v>
@@ -14041,10 +14041,10 @@
         <v>0.3325075429136386</v>
       </c>
       <c r="J64" t="n">
-        <v>28635</v>
+        <v>28641</v>
       </c>
       <c r="K64" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65">
@@ -17056,7 +17056,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -19938,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -22820,7 +22820,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3286,10 +3286,10 @@
         <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17483</v>
+        <v>17494</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3286,7 +3286,7 @@
         <v>0.02116089372266225</v>
       </c>
       <c r="J64" t="n">
-        <v>17494</v>
+        <v>17491</v>
       </c>
       <c r="K64" t="n">
         <v>9</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3591,60 +3591,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>152874</v>
+        <v>160472</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>3.115905450964996e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>12033</v>
+        <v>50052</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.7630086264623627</v>
+        <v>0.02075865600504195</v>
       </c>
       <c r="J73" t="n">
-        <v>4773</v>
+        <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>6859</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04734782391943766</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3653,13 +3653,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.7678282009724473</v>
       </c>
       <c r="J74" t="n">
-        <v>4730</v>
+        <v>4773</v>
       </c>
       <c r="K74" t="n">
-        <v>8111</v>
+        <v>6859</v>
       </c>
     </row>
     <row r="75">
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E75" t="n">
         <v>4</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J75" t="n">
         <v>4730</v>
@@ -3702,7 +3702,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
         <v>38207</v>
@@ -3730,16 +3730,16 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>10235</v>
+        <v>4730</v>
       </c>
       <c r="K76" t="n">
-        <v>3318</v>
+        <v>8111</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
         <v>38207</v>
@@ -3767,29 +3767,29 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>13721</v>
+        <v>10235</v>
       </c>
       <c r="K77" t="n">
-        <v>361</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>153028</v>
+        <v>159858</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-0.04272541880919316</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F78" t="n">
         <v>38207</v>
@@ -3804,32 +3804,32 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>14567</v>
+        <v>13721</v>
       </c>
       <c r="K78" t="n">
-        <v>81</v>
+        <v>361</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>156726</v>
+        <v>153028</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.02416551219384688</v>
+        <v>-0.04272541880919316</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>51022</v>
+        <v>38207</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3838,35 +3838,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.3354097416703745</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>15253</v>
+        <v>14567</v>
       </c>
       <c r="K79" t="n">
-        <v>475</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>160467</v>
+        <v>156726</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.0238696833965009</v>
+        <v>0.02416551219384688</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>51392</v>
+        <v>51022</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3875,35 +3875,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.007251773744659166</v>
+        <v>0.3354097416703745</v>
       </c>
       <c r="J80" t="n">
-        <v>16702</v>
+        <v>15253</v>
       </c>
       <c r="K80" t="n">
-        <v>46</v>
+        <v>475</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>152874</v>
+        <v>160467</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>0.0238696833965009</v>
       </c>
       <c r="E81" t="n">
         <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>12033</v>
+        <v>51392</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3912,35 +3912,35 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.765858499377335</v>
+        <v>0.007251773744659166</v>
       </c>
       <c r="J81" t="n">
-        <v>3662</v>
+        <v>16702</v>
       </c>
       <c r="K81" t="n">
-        <v>8545</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04731814017835443</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3949,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.765858499377335</v>
       </c>
       <c r="J82" t="n">
-        <v>4730</v>
+        <v>3662</v>
       </c>
       <c r="K82" t="n">
-        <v>8150</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="83">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J83" t="n">
         <v>4730</v>
@@ -3998,7 +3998,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>38207</v>
@@ -4026,16 +4026,16 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>10614</v>
+        <v>4730</v>
       </c>
       <c r="K84" t="n">
-        <v>2993</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>38207</v>
@@ -4063,29 +4063,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>13731</v>
+        <v>10614</v>
       </c>
       <c r="K85" t="n">
-        <v>448</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>153028</v>
+        <v>159858</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.04272541880919316</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F86" t="n">
         <v>38207</v>
@@ -4100,32 +4100,32 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>14569</v>
+        <v>13731</v>
       </c>
       <c r="K86" t="n">
-        <v>161</v>
+        <v>448</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>156789</v>
+        <v>153028</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02457720155788483</v>
+        <v>-0.04272541880919316</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F87" t="n">
-        <v>50754</v>
+        <v>38207</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4134,35 +4134,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.3283953202292774</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>15510</v>
+        <v>14569</v>
       </c>
       <c r="K87" t="n">
-        <v>298</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>160467</v>
+        <v>156789</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02345827832309665</v>
+        <v>0.02457720155788483</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>51392</v>
+        <v>50754</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4171,35 +4171,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01257043779800607</v>
+        <v>0.3283953202292774</v>
       </c>
       <c r="J88" t="n">
-        <v>16702</v>
+        <v>15510</v>
       </c>
       <c r="K88" t="n">
-        <v>141</v>
+        <v>298</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>152874</v>
+        <v>160467</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>0.02345827832309665</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>12033</v>
+        <v>51392</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4208,35 +4208,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.765858499377335</v>
+        <v>0.01257043779800607</v>
       </c>
       <c r="J89" t="n">
-        <v>3662</v>
+        <v>16702</v>
       </c>
       <c r="K89" t="n">
-        <v>8545</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04731814017835443</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -4245,19 +4245,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.765858499377335</v>
       </c>
       <c r="J90" t="n">
-        <v>4730</v>
+        <v>3662</v>
       </c>
       <c r="K90" t="n">
-        <v>8228</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4267,10 +4267,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>38207</v>
@@ -4282,19 +4282,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J91" t="n">
-        <v>11517</v>
+        <v>4730</v>
       </c>
       <c r="K91" t="n">
-        <v>2170</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>38207</v>
@@ -4322,29 +4322,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>13931</v>
+        <v>11517</v>
       </c>
       <c r="K92" t="n">
-        <v>376</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>154830</v>
+        <v>159858</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.03145291446158466</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>38207</v>
@@ -4359,32 +4359,32 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>14569</v>
+        <v>13931</v>
       </c>
       <c r="K93" t="n">
-        <v>259</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>160191</v>
+        <v>154830</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.03462507266033715</v>
+        <v>-0.03145291446158466</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>50754</v>
+        <v>38207</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -4393,71 +4393,108 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.3283953202292774</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>15886</v>
+        <v>14569</v>
       </c>
       <c r="K94" t="n">
-        <v>14</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>160467</v>
+        <v>160191</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.001722943236511414</v>
+        <v>0.03462507266033715</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
+        <v>50754</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.3283953202292774</v>
+      </c>
+      <c r="J95" t="n">
+        <v>15886</v>
+      </c>
+      <c r="K95" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>160467</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.001722943236511414</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
         <v>51427</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>1776</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.04825235449422706</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>16723</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>7593</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>39394</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>1776</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>13061</v>
       </c>
     </row>
@@ -4473,7 +4510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7176,60 +7213,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>195596</v>
+        <v>276851</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.3013779850986163</v>
+        <v>-0.01115460721352697</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>150804</v>
+        <v>196403</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>50527</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>6306</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.2692648747655944</v>
+        <v>0.22707912372258</v>
       </c>
       <c r="J73" t="n">
-        <v>4167</v>
+        <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>7562</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>186047</v>
+        <v>195596</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.04882001676925909</v>
+        <v>-0.2934972241386161</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>145022</v>
+        <v>150804</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -7238,13 +7275,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.03834115805946792</v>
+        <v>-0.4044922522864048</v>
       </c>
       <c r="J74" t="n">
-        <v>3624</v>
+        <v>4167</v>
       </c>
       <c r="K74" t="n">
-        <v>9077</v>
+        <v>7562</v>
       </c>
     </row>
     <row r="75">
@@ -7260,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>-0.04882001676925909</v>
       </c>
       <c r="E75" t="n">
         <v>4</v>
@@ -7275,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>-0.03834115805946792</v>
       </c>
       <c r="J75" t="n">
         <v>3624</v>
@@ -7287,23 +7324,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>201697</v>
+        <v>186047</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.08411852918886088</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>139905</v>
+        <v>145022</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -7312,35 +7349,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>-0.03528430169215705</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>13526</v>
+        <v>3624</v>
       </c>
       <c r="K76" t="n">
-        <v>52</v>
+        <v>9077</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0.08411852918886088</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>158599</v>
+        <v>139905</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -7349,35 +7386,35 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1336192416282477</v>
+        <v>-0.03528430169215705</v>
       </c>
       <c r="J77" t="n">
-        <v>14562</v>
+        <v>13526</v>
       </c>
       <c r="K77" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>264414</v>
+        <v>223030</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.1855535129803166</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F78" t="n">
-        <v>200191</v>
+        <v>158599</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -7386,35 +7423,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.2622462941128254</v>
+        <v>0.1336192416282477</v>
       </c>
       <c r="J78" t="n">
-        <v>15164</v>
+        <v>14562</v>
       </c>
       <c r="K78" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>280969</v>
+        <v>264414</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.06261014923566831</v>
+        <v>0.1855535129803166</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>208147</v>
+        <v>200191</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -7423,35 +7460,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.03974204634573982</v>
+        <v>0.2622462941128254</v>
       </c>
       <c r="J79" t="n">
-        <v>16288</v>
+        <v>15164</v>
       </c>
       <c r="K79" t="n">
-        <v>25</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>279974</v>
+        <v>280969</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.003541315945887269</v>
+        <v>0.06261014923566831</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>239255</v>
+        <v>208147</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -7460,35 +7497,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.1494520699313466</v>
+        <v>0.03974204634573982</v>
       </c>
       <c r="J80" t="n">
-        <v>17585</v>
+        <v>16288</v>
       </c>
       <c r="K80" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>190349</v>
+        <v>279974</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.3201190110510262</v>
+        <v>-0.003541315945887269</v>
       </c>
       <c r="E81" t="n">
         <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>136031</v>
+        <v>239255</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -7497,35 +7534,35 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.4314392593676203</v>
+        <v>0.1494520699313466</v>
       </c>
       <c r="J81" t="n">
-        <v>3632</v>
+        <v>17585</v>
       </c>
       <c r="K81" t="n">
-        <v>8333</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>201697</v>
+        <v>190349</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.05961680912429275</v>
+        <v>-0.3201190110510262</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>137131</v>
+        <v>136031</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -7534,13 +7571,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.008086392072395263</v>
+        <v>-0.4314392593676203</v>
       </c>
       <c r="J82" t="n">
-        <v>4596</v>
+        <v>3632</v>
       </c>
       <c r="K82" t="n">
-        <v>8459</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="83">
@@ -7556,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.05961680912429275</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -7571,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>0.008086392072395263</v>
       </c>
       <c r="J83" t="n">
         <v>4596</v>
@@ -7583,7 +7620,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -7596,10 +7633,10 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>139905</v>
+        <v>137131</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7608,35 +7645,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02022883228445793</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>13526</v>
+        <v>4596</v>
       </c>
       <c r="K84" t="n">
-        <v>139</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>158599</v>
+        <v>139905</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7645,35 +7682,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1336192416282477</v>
+        <v>0.02022883228445793</v>
       </c>
       <c r="J85" t="n">
-        <v>14722</v>
+        <v>13526</v>
       </c>
       <c r="K85" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>264805</v>
+        <v>223030</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.1873066403622831</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E86" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F86" t="n">
-        <v>194280</v>
+        <v>158599</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7682,35 +7719,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.2249761978322688</v>
+        <v>0.1336192416282477</v>
       </c>
       <c r="J86" t="n">
-        <v>15357</v>
+        <v>14722</v>
       </c>
       <c r="K86" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>280921</v>
+        <v>264805</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.06085987802345122</v>
+        <v>0.1873066403622831</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F87" t="n">
-        <v>193280</v>
+        <v>194280</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7719,35 +7756,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>-0.005147210212065061</v>
+        <v>0.2249761978322688</v>
       </c>
       <c r="J87" t="n">
-        <v>16288</v>
+        <v>15357</v>
       </c>
       <c r="K87" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>279057</v>
+        <v>280921</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.006635317402401386</v>
+        <v>0.06085987802345122</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>239263</v>
+        <v>193280</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -7756,35 +7793,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.2379087334437086</v>
+        <v>-0.005147210212065061</v>
       </c>
       <c r="J88" t="n">
-        <v>17672</v>
+        <v>16288</v>
       </c>
       <c r="K88" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>190349</v>
+        <v>279057</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.3178848765664363</v>
+        <v>-0.006635317402401386</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>136031</v>
+        <v>239263</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -7793,35 +7830,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.4314582697700856</v>
+        <v>0.2379087334437086</v>
       </c>
       <c r="J89" t="n">
-        <v>3632</v>
+        <v>17672</v>
       </c>
       <c r="K89" t="n">
-        <v>8333</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>201697</v>
+        <v>190349</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.05961680912429275</v>
+        <v>-0.3178848765664363</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>137131</v>
+        <v>136031</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -7830,19 +7867,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.008086392072395263</v>
+        <v>-0.4314582697700856</v>
       </c>
       <c r="J90" t="n">
-        <v>5832</v>
+        <v>3632</v>
       </c>
       <c r="K90" t="n">
-        <v>7409</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -7852,13 +7889,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.05961680912429275</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>140221</v>
+        <v>137131</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -7867,35 +7904,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.02253319818275955</v>
+        <v>0.008086392072395263</v>
       </c>
       <c r="J91" t="n">
-        <v>13526</v>
+        <v>5832</v>
       </c>
       <c r="K91" t="n">
-        <v>201</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>158599</v>
+        <v>140221</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -7904,35 +7941,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.131064533843005</v>
+        <v>0.02253319818275955</v>
       </c>
       <c r="J92" t="n">
-        <v>14777</v>
+        <v>13526</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>264838</v>
+        <v>223030</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.1874546025198404</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>194280</v>
+        <v>158599</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -7941,35 +7978,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.2249761978322688</v>
+        <v>0.131064533843005</v>
       </c>
       <c r="J93" t="n">
-        <v>15421</v>
+        <v>14777</v>
       </c>
       <c r="K93" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>282361</v>
+        <v>264838</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.06616497632514971</v>
+        <v>0.1874546025198404</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>193280</v>
+        <v>194280</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -7978,71 +8015,108 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>-0.005147210212065061</v>
+        <v>0.2249761978322688</v>
       </c>
       <c r="J94" t="n">
-        <v>16354</v>
+        <v>15421</v>
       </c>
       <c r="K94" t="n">
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>277864</v>
+        <v>282361</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>-0.0159264204334168</v>
+        <v>0.06616497632514971</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
+        <v>193280</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>-0.005147210212065061</v>
+      </c>
+      <c r="J95" t="n">
+        <v>16354</v>
+      </c>
+      <c r="K95" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>277864</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.0159264204334168</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
         <v>247810</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>1193</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.2883019453642384</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>17787</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>88824</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>111779</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>1193</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>14155</v>
       </c>
     </row>
@@ -8058,7 +8132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10761,44 +10835,44 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>44862</v>
+        <v>50003</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.007089484602525629</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>36001</v>
+        <v>36403</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>18266</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>0.4830719982637947</v>
       </c>
       <c r="J73" t="n">
-        <v>659</v>
+        <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>2065</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -10808,13 +10882,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>-0.1028138311701298</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -10823,13 +10897,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.341473229801167</v>
       </c>
       <c r="J74" t="n">
-        <v>230</v>
+        <v>659</v>
       </c>
       <c r="K74" t="n">
-        <v>2660</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="75">
@@ -10860,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J75" t="n">
         <v>230</v>
@@ -10872,7 +10946,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -10885,7 +10959,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
         <v>8468</v>
@@ -10900,16 +10974,16 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>753</v>
+        <v>230</v>
       </c>
       <c r="K76" t="n">
-        <v>2199</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -10922,7 +10996,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
         <v>8468</v>
@@ -10937,32 +11011,32 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>3007</v>
+        <v>753</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>46293</v>
+        <v>44862</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.03189781998127592</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F78" t="n">
-        <v>14963</v>
+        <v>8468</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -10971,35 +11045,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.7670051960321209</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>3244</v>
+        <v>3007</v>
       </c>
       <c r="K78" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>-0.000216015380295077</v>
+        <v>0.03189781998127592</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>36656</v>
+        <v>14963</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -11008,35 +11082,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>1.449776114415558</v>
+        <v>0.7670051960321209</v>
       </c>
       <c r="J79" t="n">
-        <v>3774</v>
+        <v>3244</v>
       </c>
       <c r="K79" t="n">
-        <v>11</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>49651</v>
+        <v>46283</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.07276969945768424</v>
+        <v>-0.000216015380295077</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>36862</v>
+        <v>36656</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -11045,35 +11119,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.00561981667394151</v>
+        <v>1.449776114415558</v>
       </c>
       <c r="J80" t="n">
-        <v>3877</v>
+        <v>3774</v>
       </c>
       <c r="K80" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>44862</v>
+        <v>49651</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.07276969945768424</v>
       </c>
       <c r="E81" t="n">
         <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>36001</v>
+        <v>36862</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -11082,19 +11156,19 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>0.00561981667394151</v>
       </c>
       <c r="J81" t="n">
-        <v>230</v>
+        <v>3877</v>
       </c>
       <c r="K81" t="n">
-        <v>2574</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -11104,13 +11178,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>-0.09645324364061147</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -11119,13 +11193,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.02335738701101405</v>
       </c>
       <c r="J82" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K82" t="n">
-        <v>2670</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="83">
@@ -11156,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J83" t="n">
         <v>225</v>
@@ -11168,7 +11242,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -11181,7 +11255,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>8468</v>
@@ -11196,32 +11270,32 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>2952</v>
+        <v>225</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>48086</v>
+        <v>44862</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.07186482992287459</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>11249</v>
+        <v>8468</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11230,10 +11304,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.3284128483703354</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>3036</v>
+        <v>2952</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -11242,23 +11316,23 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>46293</v>
+        <v>48086</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.03728736014640436</v>
+        <v>0.07186482992287459</v>
       </c>
       <c r="E86" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F86" t="n">
-        <v>14963</v>
+        <v>11249</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11267,35 +11341,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.3301626811272113</v>
+        <v>0.3284128483703354</v>
       </c>
       <c r="J86" t="n">
-        <v>3403</v>
+        <v>3036</v>
       </c>
       <c r="K86" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.000216015380295077</v>
+        <v>-0.03728736014640436</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F87" t="n">
-        <v>50754</v>
+        <v>14963</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11304,35 +11378,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>2.391966851567199</v>
+        <v>0.3301626811272113</v>
       </c>
       <c r="J87" t="n">
-        <v>3774</v>
+        <v>3403</v>
       </c>
       <c r="K87" t="n">
-        <v>43</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>49651</v>
+        <v>46283</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.07276969945768424</v>
+        <v>-0.000216015380295077</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>36862</v>
+        <v>50754</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11341,35 +11415,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.2737124167553296</v>
+        <v>2.391966851567199</v>
       </c>
       <c r="J88" t="n">
-        <v>3877</v>
+        <v>3774</v>
       </c>
       <c r="K88" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>44862</v>
+        <v>49651</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.07276969945768424</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>36001</v>
+        <v>36862</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11378,19 +11452,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>-0.2737124167553296</v>
       </c>
       <c r="J89" t="n">
-        <v>230</v>
+        <v>3877</v>
       </c>
       <c r="K89" t="n">
-        <v>2574</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -11400,13 +11474,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0</v>
+        <v>-0.09645324364061147</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11415,19 +11489,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.02335738701101405</v>
       </c>
       <c r="J90" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K90" t="n">
-        <v>2673</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -11440,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>8468</v>
@@ -11452,35 +11526,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J91" t="n">
-        <v>2952</v>
+        <v>225</v>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>48086</v>
+        <v>44862</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.07186482992287459</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>14963</v>
+        <v>8468</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11489,35 +11563,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.7670051960321209</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>3036</v>
+        <v>2952</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>46293</v>
+        <v>48086</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.03728736014640436</v>
+        <v>0.07186482992287459</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>19193</v>
+        <v>14963</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11526,35 +11600,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.2826973200561385</v>
+        <v>0.7670051960321209</v>
       </c>
       <c r="J93" t="n">
-        <v>3403</v>
+        <v>3036</v>
       </c>
       <c r="K93" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>46924</v>
+        <v>46293</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01363057049661936</v>
+        <v>-0.03728736014640436</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>50754</v>
+        <v>19193</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11563,71 +11637,108 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.644401604751732</v>
+        <v>0.2826973200561385</v>
       </c>
       <c r="J94" t="n">
-        <v>3774</v>
+        <v>3403</v>
       </c>
       <c r="K94" t="n">
-        <v>68</v>
+        <v>262</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>49651</v>
+        <v>46924</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.05811525019179951</v>
+        <v>0.01363057049661936</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
+        <v>50754</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>1.644401604751732</v>
+      </c>
+      <c r="J95" t="n">
+        <v>3774</v>
+      </c>
+      <c r="K95" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>49651</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.05811525019179951</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
         <v>36628</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>17602</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.06848721283051581</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>3928</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>4789</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>627</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>17602</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>3698</v>
       </c>
     </row>
@@ -11643,7 +11754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14346,60 +14457,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>240624</v>
+        <v>263111</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.0781890481699702</v>
+        <v>0.007956817885792656</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>42233</v>
+        <v>231867</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2645</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.7600302284749961</v>
+        <v>0.3325075429136386</v>
       </c>
       <c r="J73" t="n">
-        <v>12553</v>
+        <v>28710</v>
       </c>
       <c r="K73" t="n">
-        <v>10373</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>243285</v>
+        <v>240624</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.01105874725713146</v>
+        <v>-0.08546583001090795</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>162649</v>
+        <v>42233</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -14408,13 +14519,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.851230080742547</v>
+        <v>-0.8199111346114485</v>
       </c>
       <c r="J74" t="n">
-        <v>8096</v>
+        <v>12553</v>
       </c>
       <c r="K74" t="n">
-        <v>17287</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="75">
@@ -14430,7 +14541,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.01105874725713146</v>
       </c>
       <c r="E75" t="n">
         <v>4</v>
@@ -14445,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>2.851230080742547</v>
       </c>
       <c r="J75" t="n">
         <v>8096</v>
@@ -14457,23 +14568,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>243430</v>
+        <v>243285</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.0005960087962677518</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>203597</v>
+        <v>162649</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -14482,35 +14593,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.2517568506415656</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>25933</v>
+        <v>8096</v>
       </c>
       <c r="K76" t="n">
-        <v>325</v>
+        <v>17287</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>244292</v>
+        <v>243430</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.003541059031343713</v>
+        <v>0.0005960087962677518</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>194558</v>
+        <v>203597</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -14519,35 +14630,35 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>-0.04439652843607715</v>
+        <v>0.2517568506415656</v>
       </c>
       <c r="J77" t="n">
-        <v>26195</v>
+        <v>25933</v>
       </c>
       <c r="K77" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>245427</v>
+        <v>244292</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.004646079282170517</v>
+        <v>0.003541059031343713</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F78" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -14556,35 +14667,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.04439652843607715</v>
       </c>
       <c r="J78" t="n">
-        <v>26640</v>
+        <v>26195</v>
       </c>
       <c r="K78" t="n">
-        <v>246</v>
+        <v>322</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>255354</v>
+        <v>245427</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.04044787248346759</v>
+        <v>0.004646079282170517</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -14593,35 +14704,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J79" t="n">
-        <v>27559</v>
+        <v>26640</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>263205</v>
+        <v>255354</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.03074555323198383</v>
+        <v>0.04044787248346759</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>239305</v>
+        <v>194288</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -14630,35 +14741,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.2317024211479865</v>
+        <v>-0.002387639728271195</v>
       </c>
       <c r="J80" t="n">
-        <v>27923</v>
+        <v>27559</v>
       </c>
       <c r="K80" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>242066</v>
+        <v>263205</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.08031382382553523</v>
+        <v>0.03074555323198383</v>
       </c>
       <c r="E81" t="n">
         <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>42233</v>
+        <v>239305</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -14667,35 +14778,35 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.8235181045109797</v>
+        <v>0.2317024211479865</v>
       </c>
       <c r="J81" t="n">
-        <v>8264</v>
+        <v>27923</v>
       </c>
       <c r="K81" t="n">
-        <v>17043</v>
+        <v>376</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>243285</v>
+        <v>242066</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.005035816678096056</v>
+        <v>-0.08031382382553523</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>192466</v>
+        <v>42233</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -14704,13 +14815,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>3.557241967182061</v>
+        <v>-0.8235181045109797</v>
       </c>
       <c r="J82" t="n">
-        <v>8093</v>
+        <v>8264</v>
       </c>
       <c r="K82" t="n">
-        <v>17836</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="83">
@@ -14726,7 +14837,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.005035816678096056</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -14741,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>3.557241967182061</v>
       </c>
       <c r="J83" t="n">
         <v>8093</v>
@@ -14753,23 +14864,23 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>243430</v>
+        <v>243285</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.0005960087962677518</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>195134</v>
+        <v>192466</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -14778,35 +14889,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.01386218864630636</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>25930</v>
+        <v>8093</v>
       </c>
       <c r="K84" t="n">
-        <v>369</v>
+        <v>17836</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>244292</v>
+        <v>243430</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.003541059031343713</v>
+        <v>0.0005960087962677518</v>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>194558</v>
+        <v>195134</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -14815,35 +14926,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>-0.002951817725255465</v>
+        <v>0.01386218864630636</v>
       </c>
       <c r="J85" t="n">
-        <v>26319</v>
+        <v>25930</v>
       </c>
       <c r="K85" t="n">
-        <v>200</v>
+        <v>369</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>245427</v>
+        <v>244292</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.004646079282170517</v>
+        <v>0.003541059031343713</v>
       </c>
       <c r="E86" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F86" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -14852,35 +14963,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.002951817725255465</v>
       </c>
       <c r="J86" t="n">
-        <v>26640</v>
+        <v>26319</v>
       </c>
       <c r="K86" t="n">
-        <v>287</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>255354</v>
+        <v>245427</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.04044787248346759</v>
+        <v>0.004646079282170517</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F87" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -14889,35 +15000,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J87" t="n">
-        <v>27559</v>
+        <v>26640</v>
       </c>
       <c r="K87" t="n">
-        <v>51</v>
+        <v>287</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>260851</v>
+        <v>255354</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02152697823413771</v>
+        <v>0.04044787248346759</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>236724</v>
+        <v>194288</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -14926,35 +15037,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.2184180186115458</v>
+        <v>-0.002387639728271195</v>
       </c>
       <c r="J88" t="n">
-        <v>27923</v>
+        <v>27559</v>
       </c>
       <c r="K88" t="n">
-        <v>454</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>242066</v>
+        <v>260851</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.07201429168375816</v>
+        <v>0.02152697823413771</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>42233</v>
+        <v>236724</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -14963,35 +15074,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.82159392372552</v>
+        <v>0.2184180186115458</v>
       </c>
       <c r="J89" t="n">
-        <v>8264</v>
+        <v>27923</v>
       </c>
       <c r="K89" t="n">
-        <v>17043</v>
+        <v>454</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>243285</v>
+        <v>242066</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.005035816678096056</v>
+        <v>-0.07201429168375816</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>192466</v>
+        <v>42233</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -15000,35 +15111,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>3.557241967182061</v>
+        <v>-0.82159392372552</v>
       </c>
       <c r="J90" t="n">
-        <v>8092</v>
+        <v>8264</v>
       </c>
       <c r="K90" t="n">
-        <v>17874</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>243440</v>
+        <v>243285</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.0006371128511827691</v>
+        <v>0.005035816678096056</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>195134</v>
+        <v>192466</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -15037,35 +15148,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.01386218864630636</v>
+        <v>3.557241967182061</v>
       </c>
       <c r="J91" t="n">
-        <v>25929</v>
+        <v>8092</v>
       </c>
       <c r="K91" t="n">
-        <v>399</v>
+        <v>17874</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>250208</v>
+        <v>243440</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.02780151166611896</v>
+        <v>0.0006371128511827691</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>194558</v>
+        <v>195134</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -15074,35 +15185,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>-0.002951817725255465</v>
+        <v>0.01386218864630636</v>
       </c>
       <c r="J92" t="n">
-        <v>26584</v>
+        <v>25929</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>245427</v>
+        <v>250208</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.01910810205908684</v>
+        <v>0.02780151166611896</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -15111,35 +15222,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.002951817725255465</v>
       </c>
       <c r="J93" t="n">
-        <v>26898</v>
+        <v>26584</v>
       </c>
       <c r="K93" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>258366</v>
+        <v>245427</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.05272036084049432</v>
+        <v>-0.01910810205908684</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -15148,71 +15259,108 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J94" t="n">
-        <v>27560</v>
+        <v>26898</v>
       </c>
       <c r="K94" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>260851</v>
+        <v>258366</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.009618138609569371</v>
+        <v>0.05272036084049432</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
+        <v>194288</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>-0.002387639728271195</v>
+      </c>
+      <c r="J95" t="n">
+        <v>27560</v>
+      </c>
+      <c r="K95" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>260851</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.009618138609569371</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
         <v>234378</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>2645</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.2199569710944577</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>28255</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>181</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>18785</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>192145</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>2645</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>19991</v>
       </c>
     </row>
@@ -15228,7 +15376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17339,20 +17487,20 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17367,10 +17515,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
@@ -17386,7 +17534,7 @@
         <v>0</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E58" t="n">
         <v>4</v>
@@ -17413,7 +17561,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -17426,7 +17574,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -17450,7 +17598,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -17463,7 +17611,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -17487,7 +17635,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -17500,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -17515,20 +17663,20 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K61" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6707</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -17537,7 +17685,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -17552,29 +17700,29 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7109</v>
+        <v>6707</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.05993737885790965</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -17592,26 +17740,26 @@
         <v>386</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-1</v>
+        <v>0.05993737885790965</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17626,10 +17774,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -17645,7 +17793,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -17672,7 +17820,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -17685,7 +17833,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -17703,13 +17851,13 @@
         <v>365</v>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -17722,7 +17870,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -17746,11 +17894,11 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6588</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -17759,7 +17907,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -17774,29 +17922,29 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K68" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6707</v>
+        <v>6588</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.01806314511232544</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -17811,29 +17959,29 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>7109</v>
+        <v>6707</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.05993737885790965</v>
+        <v>0.01806314511232544</v>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -17851,26 +17999,26 @@
         <v>386</v>
       </c>
       <c r="K70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>-1</v>
+        <v>0.05993737885790965</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -17885,16 +18033,16 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -17904,10 +18052,10 @@
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17931,7 +18079,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -17944,7 +18092,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -17968,11 +18116,11 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6588</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -17981,7 +18129,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -17996,29 +18144,29 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="K74" t="n">
-        <v>352</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7109</v>
+        <v>6588</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.07908318154219794</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -18033,16 +18181,16 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>386</v>
+        <v>30</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -18052,7 +18200,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0</v>
+        <v>0.07908318154219794</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -18073,28 +18221,65 @@
         <v>386</v>
       </c>
       <c r="K76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7109</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>386</v>
+      </c>
+      <c r="K77" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B78" s="4" t="n">
         <v>7109</v>
       </c>
-      <c r="F77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="n">
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -18110,7 +18295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -20221,7 +20406,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -20234,7 +20419,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20295,7 +20480,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -20308,7 +20493,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -20332,7 +20517,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -20345,7 +20530,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -20369,7 +20554,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -20382,7 +20567,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -20406,7 +20591,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -20419,7 +20604,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -20443,7 +20628,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -20456,7 +20641,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -20480,7 +20665,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -20493,7 +20678,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20511,7 +20696,7 @@
         <v>185</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -20554,7 +20739,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -20567,7 +20752,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -20585,13 +20770,13 @@
         <v>185</v>
       </c>
       <c r="K66" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -20604,7 +20789,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -20628,7 +20813,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -20641,7 +20826,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -20665,7 +20850,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -20678,7 +20863,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -20702,7 +20887,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -20715,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -20739,7 +20924,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -20752,7 +20937,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -20776,7 +20961,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -20789,7 +20974,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -20813,7 +20998,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -20826,7 +21011,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -20850,7 +21035,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -20863,7 +21048,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -20887,7 +21072,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -20900,7 +21085,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -20924,7 +21109,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -20959,24 +21144,61 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>185</v>
+      </c>
+      <c r="K77" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="n">
+      <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20992,7 +21214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -23103,7 +23325,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -23116,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -23177,7 +23399,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -23190,7 +23412,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -23214,7 +23436,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -23227,7 +23449,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -23251,7 +23473,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -23264,7 +23486,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -23288,7 +23510,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -23301,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -23325,7 +23547,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -23338,7 +23560,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23362,7 +23584,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -23375,7 +23597,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -23393,7 +23615,7 @@
         <v>119</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -23436,7 +23658,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -23449,7 +23671,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -23467,13 +23689,13 @@
         <v>119</v>
       </c>
       <c r="K66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -23486,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -23510,7 +23732,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -23523,7 +23745,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -23547,7 +23769,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -23560,7 +23782,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -23584,7 +23806,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -23597,7 +23819,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -23621,7 +23843,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -23634,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -23658,7 +23880,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -23671,7 +23893,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -23695,7 +23917,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -23708,7 +23930,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -23732,7 +23954,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -23745,7 +23967,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -23769,7 +23991,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -23782,7 +24004,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -23806,7 +24028,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -23841,24 +24063,61 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>119</v>
+      </c>
+      <c r="K77" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="n">
+      <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -14485,10 +14485,10 @@
         <v>0.3325075429136386</v>
       </c>
       <c r="J73" t="n">
-        <v>28710</v>
+        <v>28757</v>
       </c>
       <c r="K73" t="n">
-        <v>179</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7229,16 +7229,16 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>196403</v>
+        <v>243101</v>
       </c>
       <c r="G73" t="n">
-        <v>50527</v>
+        <v>4444</v>
       </c>
       <c r="H73" t="n">
-        <v>6306</v>
+        <v>14889</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.22707912372258</v>
+        <v>0.2716489075605821</v>
       </c>
       <c r="J73" t="n">
         <v>18497</v>
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.4044922522864048</v>
+        <v>-0.4253640915430165</v>
       </c>
       <c r="J74" t="n">
         <v>4167</v>
@@ -14485,10 +14485,10 @@
         <v>0.3325075429136386</v>
       </c>
       <c r="J73" t="n">
-        <v>28757</v>
+        <v>28773</v>
       </c>
       <c r="K73" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -14473,22 +14473,22 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>231867</v>
+        <v>231175</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="H73" t="n">
         <v>2645</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.3325075429136386</v>
+        <v>0.3368940810145858</v>
       </c>
       <c r="J73" t="n">
-        <v>28773</v>
+        <v>28811</v>
       </c>
       <c r="K73" t="n">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74">
@@ -14519,7 +14519,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.8199111346114485</v>
+        <v>-0.8205020315873582</v>
       </c>
       <c r="J74" t="n">
         <v>12553</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -14473,22 +14473,22 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>231175</v>
+        <v>231256</v>
       </c>
       <c r="G73" t="n">
         <v>1464</v>
       </c>
       <c r="H73" t="n">
-        <v>2645</v>
+        <v>2921</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.3368940810145858</v>
+        <v>0.3389225707840653</v>
       </c>
       <c r="J73" t="n">
-        <v>28811</v>
+        <v>28792</v>
       </c>
       <c r="K73" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74">
@@ -14519,7 +14519,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.8205020315873582</v>
+        <v>-0.8207739739688764</v>
       </c>
       <c r="J74" t="n">
         <v>12553</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28792</v>
       </c>
       <c r="K73" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">
@@ -14485,10 +14485,10 @@
         <v>0.3389225707840653</v>
       </c>
       <c r="J73" t="n">
-        <v>28792</v>
+        <v>28799</v>
       </c>
       <c r="K73" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74">
@@ -14485,10 +14485,10 @@
         <v>0.3389225707840653</v>
       </c>
       <c r="J73" t="n">
-        <v>28799</v>
+        <v>28794</v>
       </c>
       <c r="K73" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74">
@@ -14485,10 +14485,10 @@
         <v>0.3389225707840653</v>
       </c>
       <c r="J73" t="n">
-        <v>28794</v>
+        <v>28832</v>
       </c>
       <c r="K73" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28832</v>
       </c>
       <c r="K73" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28832</v>
       </c>
       <c r="K73" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74">
@@ -10866,7 +10866,7 @@
         <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28832</v>
       </c>
       <c r="K73" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74">
@@ -14473,22 +14473,22 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>231256</v>
+        <v>225544</v>
       </c>
       <c r="G73" t="n">
-        <v>1464</v>
+        <v>9719</v>
       </c>
       <c r="H73" t="n">
         <v>2921</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.3389225707840653</v>
+        <v>0.3533720091139989</v>
       </c>
       <c r="J73" t="n">
-        <v>28832</v>
+        <v>28881</v>
       </c>
       <c r="K73" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
@@ -14519,7 +14519,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.8207739739688764</v>
+        <v>-0.8226875020992174</v>
       </c>
       <c r="J74" t="n">
         <v>12553</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18497</v>
       </c>
       <c r="K73" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28881</v>
       </c>
       <c r="K73" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
@@ -7241,10 +7241,10 @@
         <v>0.2716489075605821</v>
       </c>
       <c r="J73" t="n">
-        <v>18497</v>
+        <v>18510</v>
       </c>
       <c r="K73" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74">
@@ -10851,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>36403</v>
+        <v>40620</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -10860,7 +10860,7 @@
         <v>18266</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.4830719982637947</v>
+        <v>0.5974716510227335</v>
       </c>
       <c r="J73" t="n">
         <v>4100</v>
@@ -10897,7 +10897,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.341473229801167</v>
+        <v>-0.3886322725265768</v>
       </c>
       <c r="J74" t="n">
         <v>659</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3604,7 +3604,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>50052</v>
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74">
@@ -7226,7 +7226,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>243101</v>
@@ -7241,10 +7241,10 @@
         <v>0.2716489075605821</v>
       </c>
       <c r="J73" t="n">
-        <v>18510</v>
+        <v>18523</v>
       </c>
       <c r="K73" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74">
@@ -10848,7 +10848,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>40620</v>
@@ -10866,7 +10866,7 @@
         <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
@@ -14470,7 +14470,7 @@
         <v>0.007956817885792656</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>225544</v>
@@ -14488,7 +14488,7 @@
         <v>28881</v>
       </c>
       <c r="K73" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">
@@ -17500,7 +17500,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20419,7 +20419,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -23338,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18523</v>
       </c>
       <c r="K73" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74">
@@ -10866,7 +10866,7 @@
         <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28881</v>
       </c>
       <c r="K73" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
@@ -7244,7 +7244,7 @@
         <v>18523</v>
       </c>
       <c r="K73" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -10866,7 +10866,7 @@
         <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28881</v>
       </c>
       <c r="K73" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7244,7 +7244,7 @@
         <v>18523</v>
       </c>
       <c r="K73" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74">
@@ -10866,7 +10866,7 @@
         <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28881</v>
       </c>
       <c r="K73" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7241,10 +7241,10 @@
         <v>0.2716489075605821</v>
       </c>
       <c r="J73" t="n">
-        <v>18523</v>
+        <v>18561</v>
       </c>
       <c r="K73" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">
@@ -10866,7 +10866,7 @@
         <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
@@ -14488,7 +14488,7 @@
         <v>28881</v>
       </c>
       <c r="K73" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3622,7 +3622,7 @@
         <v>17491</v>
       </c>
       <c r="K73" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74">
@@ -7241,10 +7241,10 @@
         <v>0.2716489075605821</v>
       </c>
       <c r="J73" t="n">
-        <v>18561</v>
+        <v>18627</v>
       </c>
       <c r="K73" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -10866,7 +10866,7 @@
         <v>4100</v>
       </c>
       <c r="K73" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74">
@@ -14485,10 +14485,10 @@
         <v>0.3533720091139989</v>
       </c>
       <c r="J73" t="n">
-        <v>28881</v>
+        <v>28880</v>
       </c>
       <c r="K73" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7244,7 +7244,7 @@
         <v>18627</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7244,7 +7244,7 @@
         <v>18627</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3604,7 +3604,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>50052</v>
@@ -7226,7 +7226,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>243101</v>
@@ -10848,7 +10848,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>40620</v>
@@ -14470,7 +14470,7 @@
         <v>0.007956817885792656</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>225544</v>
@@ -17500,7 +17500,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20419,7 +20419,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -23338,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3604,7 +3604,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>50052</v>
@@ -3924,60 +3924,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>152874</v>
+        <v>160472</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>12033</v>
+        <v>50052</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.765858499377335</v>
+        <v>0.008483810709838106</v>
       </c>
       <c r="J82" t="n">
-        <v>3662</v>
+        <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>8545</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04734782391943766</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3986,13 +3986,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.7678282009724473</v>
       </c>
       <c r="J83" t="n">
-        <v>4730</v>
+        <v>3662</v>
       </c>
       <c r="K83" t="n">
-        <v>8150</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="84">
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J84" t="n">
         <v>4730</v>
@@ -4035,7 +4035,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>38207</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>10614</v>
+        <v>4730</v>
       </c>
       <c r="K85" t="n">
-        <v>2993</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>38207</v>
@@ -4100,29 +4100,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>13731</v>
+        <v>10614</v>
       </c>
       <c r="K86" t="n">
-        <v>448</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>153028</v>
+        <v>159858</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.04272541880919316</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F87" t="n">
         <v>38207</v>
@@ -4137,32 +4137,32 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>14569</v>
+        <v>13731</v>
       </c>
       <c r="K87" t="n">
-        <v>161</v>
+        <v>448</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>156789</v>
+        <v>153028</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02457720155788483</v>
+        <v>-0.04272541880919316</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F88" t="n">
-        <v>50754</v>
+        <v>38207</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4171,35 +4171,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.3283953202292774</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>15510</v>
+        <v>14569</v>
       </c>
       <c r="K88" t="n">
-        <v>298</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>160467</v>
+        <v>156789</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.02345827832309665</v>
+        <v>0.02457720155788483</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>51392</v>
+        <v>50754</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4208,35 +4208,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01257043779800607</v>
+        <v>0.3283953202292774</v>
       </c>
       <c r="J89" t="n">
-        <v>16702</v>
+        <v>15510</v>
       </c>
       <c r="K89" t="n">
-        <v>141</v>
+        <v>298</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>152874</v>
+        <v>160467</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.04731814017835443</v>
+        <v>0.02345827832309665</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>12033</v>
+        <v>51392</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -4245,35 +4245,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.765858499377335</v>
+        <v>0.01257043779800607</v>
       </c>
       <c r="J90" t="n">
-        <v>3662</v>
+        <v>16702</v>
       </c>
       <c r="K90" t="n">
-        <v>8545</v>
+        <v>141</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>159858</v>
+        <v>152874</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.04568468150241375</v>
+        <v>-0.04731814017835443</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>38207</v>
+        <v>12033</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4282,19 +4282,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2.175184908169201</v>
+        <v>-0.765858499377335</v>
       </c>
       <c r="J91" t="n">
-        <v>4730</v>
+        <v>3662</v>
       </c>
       <c r="K91" t="n">
-        <v>8228</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.04568468150241375</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>38207</v>
@@ -4319,19 +4319,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.175184908169201</v>
       </c>
       <c r="J92" t="n">
-        <v>11517</v>
+        <v>4730</v>
       </c>
       <c r="K92" t="n">
-        <v>2170</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
         <v>38207</v>
@@ -4359,29 +4359,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>13931</v>
+        <v>11517</v>
       </c>
       <c r="K93" t="n">
-        <v>376</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>154830</v>
+        <v>159858</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.03145291446158466</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>38207</v>
@@ -4396,32 +4396,32 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>14569</v>
+        <v>13931</v>
       </c>
       <c r="K94" t="n">
-        <v>259</v>
+        <v>376</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>160191</v>
+        <v>154830</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.03462507266033715</v>
+        <v>-0.03145291446158466</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F95" t="n">
-        <v>50754</v>
+        <v>38207</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4430,71 +4430,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.3283953202292774</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>15886</v>
+        <v>14569</v>
       </c>
       <c r="K95" t="n">
-        <v>14</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>160467</v>
+        <v>160191</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.001722943236511414</v>
+        <v>0.03462507266033715</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
+        <v>50754</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.3283953202292774</v>
+      </c>
+      <c r="J96" t="n">
+        <v>15886</v>
+      </c>
+      <c r="K96" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>160467</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.001722943236511414</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
         <v>51427</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>1776</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.04825235449422706</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>16723</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>7593</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>39394</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>1776</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>13061</v>
       </c>
     </row>
@@ -4510,7 +4547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7226,7 +7263,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>243101</v>
@@ -7546,60 +7583,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>190349</v>
+        <v>276851</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.3201190110510262</v>
+        <v>-0.01115460721352697</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>136031</v>
+        <v>243101</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>4444</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>14889</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.4314392593676203</v>
+        <v>0.09687989801676036</v>
       </c>
       <c r="J82" t="n">
-        <v>3632</v>
+        <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>8333</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>201697</v>
+        <v>190349</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.05961680912429275</v>
+        <v>-0.312449657035734</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>137131</v>
+        <v>136031</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7608,13 +7645,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.008086392072395263</v>
+        <v>-0.4816563402607894</v>
       </c>
       <c r="J83" t="n">
-        <v>4596</v>
+        <v>3632</v>
       </c>
       <c r="K83" t="n">
-        <v>8459</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="84">
@@ -7630,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.05961680912429275</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -7645,7 +7682,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.008086392072395263</v>
       </c>
       <c r="J84" t="n">
         <v>4596</v>
@@ -7657,7 +7694,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -7670,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>139905</v>
+        <v>137131</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7682,35 +7719,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.02022883228445793</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>13526</v>
+        <v>4596</v>
       </c>
       <c r="K85" t="n">
-        <v>139</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>158599</v>
+        <v>139905</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7719,35 +7756,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.1336192416282477</v>
+        <v>0.02022883228445793</v>
       </c>
       <c r="J86" t="n">
-        <v>14722</v>
+        <v>13526</v>
       </c>
       <c r="K86" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>264805</v>
+        <v>223030</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.1873066403622831</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E87" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F87" t="n">
-        <v>194280</v>
+        <v>158599</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7756,35 +7793,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.2249761978322688</v>
+        <v>0.1336192416282477</v>
       </c>
       <c r="J87" t="n">
-        <v>15357</v>
+        <v>14722</v>
       </c>
       <c r="K87" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>280921</v>
+        <v>264805</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.06085987802345122</v>
+        <v>0.1873066403622831</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F88" t="n">
-        <v>193280</v>
+        <v>194280</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -7793,35 +7830,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.005147210212065061</v>
+        <v>0.2249761978322688</v>
       </c>
       <c r="J88" t="n">
-        <v>16288</v>
+        <v>15357</v>
       </c>
       <c r="K88" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>279057</v>
+        <v>280921</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.006635317402401386</v>
+        <v>0.06085987802345122</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>239263</v>
+        <v>193280</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -7830,35 +7867,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.2379087334437086</v>
+        <v>-0.005147210212065061</v>
       </c>
       <c r="J89" t="n">
-        <v>17672</v>
+        <v>16288</v>
       </c>
       <c r="K89" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>190349</v>
+        <v>279057</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.3178848765664363</v>
+        <v>-0.006635317402401386</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>136031</v>
+        <v>239263</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -7867,35 +7904,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.4314582697700856</v>
+        <v>0.2379087334437086</v>
       </c>
       <c r="J90" t="n">
-        <v>3632</v>
+        <v>17672</v>
       </c>
       <c r="K90" t="n">
-        <v>8333</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>201697</v>
+        <v>190349</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.05961680912429275</v>
+        <v>-0.3178848765664363</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>137131</v>
+        <v>136031</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -7904,19 +7941,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.008086392072395263</v>
+        <v>-0.4314582697700856</v>
       </c>
       <c r="J91" t="n">
-        <v>5832</v>
+        <v>3632</v>
       </c>
       <c r="K91" t="n">
-        <v>7409</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -7926,13 +7963,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.05961680912429275</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>140221</v>
+        <v>137131</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -7941,35 +7978,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.02253319818275955</v>
+        <v>0.008086392072395263</v>
       </c>
       <c r="J92" t="n">
-        <v>13526</v>
+        <v>5832</v>
       </c>
       <c r="K92" t="n">
-        <v>201</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>223030</v>
+        <v>201697</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.1057675622344408</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>158599</v>
+        <v>140221</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -7978,35 +8015,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.131064533843005</v>
+        <v>0.02253319818275955</v>
       </c>
       <c r="J93" t="n">
-        <v>14777</v>
+        <v>13526</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>264838</v>
+        <v>223030</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.1874546025198404</v>
+        <v>0.1057675622344408</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>194280</v>
+        <v>158599</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -8015,35 +8052,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.2249761978322688</v>
+        <v>0.131064533843005</v>
       </c>
       <c r="J94" t="n">
-        <v>15421</v>
+        <v>14777</v>
       </c>
       <c r="K94" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>282361</v>
+        <v>264838</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.06616497632514971</v>
+        <v>0.1874546025198404</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F95" t="n">
-        <v>193280</v>
+        <v>194280</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -8052,71 +8089,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>-0.005147210212065061</v>
+        <v>0.2249761978322688</v>
       </c>
       <c r="J95" t="n">
-        <v>16354</v>
+        <v>15421</v>
       </c>
       <c r="K95" t="n">
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>277864</v>
+        <v>282361</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>-0.0159264204334168</v>
+        <v>0.06616497632514971</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
+        <v>193280</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>-0.005147210212065061</v>
+      </c>
+      <c r="J96" t="n">
+        <v>16354</v>
+      </c>
+      <c r="K96" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>277864</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>-0.0159264204334168</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
         <v>247810</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>1193</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.2883019453642384</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>17787</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>88824</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>111779</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>1193</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>14155</v>
       </c>
     </row>
@@ -8132,7 +8206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10848,7 +10922,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>40620</v>
@@ -11168,44 +11242,44 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>44862</v>
+        <v>50003</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>36001</v>
+        <v>40620</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>18266</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>0.5974716510227335</v>
       </c>
       <c r="J82" t="n">
-        <v>230</v>
+        <v>4100</v>
       </c>
       <c r="K82" t="n">
-        <v>2574</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -11215,13 +11289,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.1028138311701298</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -11230,13 +11304,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.3886322725265768</v>
       </c>
       <c r="J83" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K83" t="n">
-        <v>2670</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="84">
@@ -11267,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J84" t="n">
         <v>225</v>
@@ -11279,7 +11353,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -11292,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>8468</v>
@@ -11307,32 +11381,32 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2952</v>
+        <v>225</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>48086</v>
+        <v>44862</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.07186482992287459</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>11249</v>
+        <v>8468</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11341,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.3284128483703354</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>3036</v>
+        <v>2952</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -11353,23 +11427,23 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>46293</v>
+        <v>48086</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.03728736014640436</v>
+        <v>0.07186482992287459</v>
       </c>
       <c r="E87" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F87" t="n">
-        <v>14963</v>
+        <v>11249</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11378,35 +11452,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.3301626811272113</v>
+        <v>0.3284128483703354</v>
       </c>
       <c r="J87" t="n">
-        <v>3403</v>
+        <v>3036</v>
       </c>
       <c r="K87" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.000216015380295077</v>
+        <v>-0.03728736014640436</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F88" t="n">
-        <v>50754</v>
+        <v>14963</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11415,35 +11489,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>2.391966851567199</v>
+        <v>0.3301626811272113</v>
       </c>
       <c r="J88" t="n">
-        <v>3774</v>
+        <v>3403</v>
       </c>
       <c r="K88" t="n">
-        <v>43</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>49651</v>
+        <v>46283</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.07276969945768424</v>
+        <v>-0.000216015380295077</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>36862</v>
+        <v>50754</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11452,35 +11526,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.2737124167553296</v>
+        <v>2.391966851567199</v>
       </c>
       <c r="J89" t="n">
-        <v>3877</v>
+        <v>3774</v>
       </c>
       <c r="K89" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>44862</v>
+        <v>49651</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.09645324364061147</v>
+        <v>0.07276969945768424</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>36001</v>
+        <v>36862</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11489,19 +11563,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.02335738701101405</v>
+        <v>-0.2737124167553296</v>
       </c>
       <c r="J90" t="n">
-        <v>230</v>
+        <v>3877</v>
       </c>
       <c r="K90" t="n">
-        <v>2574</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -11511,13 +11585,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.09645324364061147</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>8468</v>
+        <v>36001</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11526,19 +11600,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.7647843115469015</v>
+        <v>-0.02335738701101405</v>
       </c>
       <c r="J91" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K91" t="n">
-        <v>2673</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -11551,7 +11625,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>8468</v>
@@ -11563,35 +11637,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>-0.7647843115469015</v>
       </c>
       <c r="J92" t="n">
-        <v>2952</v>
+        <v>225</v>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>48086</v>
+        <v>44862</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.07186482992287459</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>14963</v>
+        <v>8468</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11600,35 +11674,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.7670051960321209</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>3036</v>
+        <v>2952</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>46293</v>
+        <v>48086</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.03728736014640436</v>
+        <v>0.07186482992287459</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>19193</v>
+        <v>14963</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11637,35 +11711,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.2826973200561385</v>
+        <v>0.7670051960321209</v>
       </c>
       <c r="J94" t="n">
-        <v>3403</v>
+        <v>3036</v>
       </c>
       <c r="K94" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>46924</v>
+        <v>46293</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.01363057049661936</v>
+        <v>-0.03728736014640436</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F95" t="n">
-        <v>50754</v>
+        <v>19193</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -11674,71 +11748,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>1.644401604751732</v>
+        <v>0.2826973200561385</v>
       </c>
       <c r="J95" t="n">
-        <v>3774</v>
+        <v>3403</v>
       </c>
       <c r="K95" t="n">
-        <v>68</v>
+        <v>262</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>49651</v>
+        <v>46924</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.05811525019179951</v>
+        <v>0.01363057049661936</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
+        <v>50754</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>1.644401604751732</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3774</v>
+      </c>
+      <c r="K96" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>49651</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.05811525019179951</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
         <v>36628</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>17602</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.06848721283051581</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>3928</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>4789</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>627</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>17602</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>3698</v>
       </c>
     </row>
@@ -11754,7 +11865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14470,7 +14581,7 @@
         <v>0.007956817885792656</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>225544</v>
@@ -14790,60 +14901,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>242066</v>
+        <v>263111</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.08031382382553523</v>
+        <v>-0.0003571360726429969</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>42233</v>
+        <v>225788</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>9719</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2921</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.8235181045109797</v>
+        <v>-0.00366477925659723</v>
       </c>
       <c r="J82" t="n">
-        <v>8264</v>
+        <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>17043</v>
+        <v>89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>243285</v>
+        <v>242066</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.005035816678096056</v>
+        <v>-0.07998525337215091</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>192466</v>
+        <v>42233</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -14852,13 +14963,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>3.557241967182061</v>
+        <v>-0.8228689583438187</v>
       </c>
       <c r="J83" t="n">
-        <v>8093</v>
+        <v>8264</v>
       </c>
       <c r="K83" t="n">
-        <v>17836</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="84">
@@ -14874,7 +14985,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.005035816678096056</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -14889,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>3.557241967182061</v>
       </c>
       <c r="J84" t="n">
         <v>8093</v>
@@ -14901,23 +15012,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>243430</v>
+        <v>243285</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.0005960087962677518</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>195134</v>
+        <v>192466</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -14926,35 +15037,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.01386218864630636</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>25930</v>
+        <v>8093</v>
       </c>
       <c r="K85" t="n">
-        <v>369</v>
+        <v>17836</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>244292</v>
+        <v>243430</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.003541059031343713</v>
+        <v>0.0005960087962677518</v>
       </c>
       <c r="E86" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>194558</v>
+        <v>195134</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -14963,35 +15074,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.002951817725255465</v>
+        <v>0.01386218864630636</v>
       </c>
       <c r="J86" t="n">
-        <v>26319</v>
+        <v>25930</v>
       </c>
       <c r="K86" t="n">
-        <v>200</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>245427</v>
+        <v>244292</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.004646079282170517</v>
+        <v>0.003541059031343713</v>
       </c>
       <c r="E87" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F87" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -15000,35 +15111,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.002951817725255465</v>
       </c>
       <c r="J87" t="n">
-        <v>26640</v>
+        <v>26319</v>
       </c>
       <c r="K87" t="n">
-        <v>287</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>255354</v>
+        <v>245427</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.04044787248346759</v>
+        <v>0.004646079282170517</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F88" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -15037,35 +15148,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J88" t="n">
-        <v>27559</v>
+        <v>26640</v>
       </c>
       <c r="K88" t="n">
-        <v>51</v>
+        <v>287</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>260851</v>
+        <v>255354</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.02152697823413771</v>
+        <v>0.04044787248346759</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>236724</v>
+        <v>194288</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -15074,35 +15185,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.2184180186115458</v>
+        <v>-0.002387639728271195</v>
       </c>
       <c r="J89" t="n">
-        <v>27923</v>
+        <v>27559</v>
       </c>
       <c r="K89" t="n">
-        <v>454</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>242066</v>
+        <v>260851</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.07201429168375816</v>
+        <v>0.02152697823413771</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>42233</v>
+        <v>236724</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -15111,35 +15222,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.82159392372552</v>
+        <v>0.2184180186115458</v>
       </c>
       <c r="J90" t="n">
-        <v>8264</v>
+        <v>27923</v>
       </c>
       <c r="K90" t="n">
-        <v>17043</v>
+        <v>454</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>243285</v>
+        <v>242066</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.005035816678096056</v>
+        <v>-0.07201429168375816</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>192466</v>
+        <v>42233</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -15148,35 +15259,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>3.557241967182061</v>
+        <v>-0.82159392372552</v>
       </c>
       <c r="J91" t="n">
-        <v>8092</v>
+        <v>8264</v>
       </c>
       <c r="K91" t="n">
-        <v>17874</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>243440</v>
+        <v>243285</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.0006371128511827691</v>
+        <v>0.005035816678096056</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>195134</v>
+        <v>192466</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -15185,35 +15296,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.01386218864630636</v>
+        <v>3.557241967182061</v>
       </c>
       <c r="J92" t="n">
-        <v>25929</v>
+        <v>8092</v>
       </c>
       <c r="K92" t="n">
-        <v>399</v>
+        <v>17874</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>250208</v>
+        <v>243440</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.02780151166611896</v>
+        <v>0.0006371128511827691</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>194558</v>
+        <v>195134</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -15222,35 +15333,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>-0.002951817725255465</v>
+        <v>0.01386218864630636</v>
       </c>
       <c r="J93" t="n">
-        <v>26584</v>
+        <v>25929</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>245427</v>
+        <v>250208</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.01910810205908684</v>
+        <v>0.02780151166611896</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>194753</v>
+        <v>194558</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -15259,35 +15370,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.001002271816116531</v>
+        <v>-0.002951817725255465</v>
       </c>
       <c r="J94" t="n">
-        <v>26898</v>
+        <v>26584</v>
       </c>
       <c r="K94" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>258366</v>
+        <v>245427</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.05272036084049432</v>
+        <v>-0.01910810205908684</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F95" t="n">
-        <v>194288</v>
+        <v>194753</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -15296,71 +15407,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>-0.002387639728271195</v>
+        <v>0.001002271816116531</v>
       </c>
       <c r="J95" t="n">
-        <v>27560</v>
+        <v>26898</v>
       </c>
       <c r="K95" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>260851</v>
+        <v>258366</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.009618138609569371</v>
+        <v>0.05272036084049432</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
+        <v>194288</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>-0.002387639728271195</v>
+      </c>
+      <c r="J96" t="n">
+        <v>27560</v>
+      </c>
+      <c r="K96" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>260851</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.009618138609569371</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
         <v>234378</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>2645</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.2199569710944577</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>28255</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>181</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>18785</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>192145</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>2645</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>19991</v>
       </c>
     </row>
@@ -15376,7 +15524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17500,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17783,20 +17931,20 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -17811,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -17830,7 +17978,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -17857,7 +18005,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -17870,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -17888,13 +18036,13 @@
         <v>365</v>
       </c>
       <c r="K67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -17907,7 +18055,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -17931,11 +18079,11 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6588</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -17944,7 +18092,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -17959,29 +18107,29 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K69" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6707</v>
+        <v>6588</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.01806314511232544</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -17996,29 +18144,29 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7109</v>
+        <v>6707</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.05993737885790965</v>
+        <v>0.01806314511232544</v>
       </c>
       <c r="E71" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -18036,26 +18184,26 @@
         <v>386</v>
       </c>
       <c r="K71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-1</v>
+        <v>0.05993737885790965</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -18070,16 +18218,16 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -18089,10 +18237,10 @@
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18116,7 +18264,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -18129,7 +18277,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -18153,11 +18301,11 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6588</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -18166,7 +18314,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -18181,29 +18329,29 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="K75" t="n">
-        <v>352</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7109</v>
+        <v>6588</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.07908318154219794</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -18218,16 +18366,16 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>386</v>
+        <v>30</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -18237,7 +18385,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0</v>
+        <v>0.07908318154219794</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -18258,28 +18406,65 @@
         <v>386</v>
       </c>
       <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7109</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>386</v>
+      </c>
+      <c r="K78" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B79" s="4" t="n">
         <v>7109</v>
       </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -18295,7 +18480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -20419,7 +20604,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20702,7 +20887,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -20715,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20733,7 +20918,7 @@
         <v>185</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
@@ -20776,7 +20961,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -20789,7 +20974,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -20807,13 +20992,13 @@
         <v>185</v>
       </c>
       <c r="K67" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -20826,7 +21011,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -20850,7 +21035,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -20863,7 +21048,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -20887,7 +21072,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -20900,7 +21085,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -20924,7 +21109,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -20937,7 +21122,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -20961,7 +21146,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -20974,7 +21159,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -20998,7 +21183,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -21011,7 +21196,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21035,7 +21220,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -21048,7 +21233,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -21072,7 +21257,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -21085,7 +21270,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -21109,7 +21294,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -21122,7 +21307,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -21146,7 +21331,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -21181,24 +21366,61 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>185</v>
+      </c>
+      <c r="K78" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21214,7 +21436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -23338,7 +23560,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -23621,7 +23843,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -23634,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23652,7 +23874,7 @@
         <v>119</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -23695,7 +23917,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -23708,7 +23930,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -23726,13 +23948,13 @@
         <v>119</v>
       </c>
       <c r="K67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -23745,7 +23967,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -23769,7 +23991,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -23782,7 +24004,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -23806,7 +24028,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -23819,7 +24041,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -23843,7 +24065,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -23856,7 +24078,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -23880,7 +24102,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -23893,7 +24115,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -23917,7 +24139,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -23930,7 +24152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -23954,7 +24176,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -23967,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -23991,7 +24213,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -24004,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -24028,7 +24250,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -24041,7 +24263,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -24065,7 +24287,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -24100,24 +24322,61 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>119</v>
+      </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83">
@@ -7596,7 +7596,7 @@
         <v>-0.01115460721352697</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -14914,25 +14914,25 @@
         <v>-0.0003571360726429969</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>225788</v>
+        <v>225954</v>
       </c>
       <c r="G82" t="n">
         <v>9719</v>
       </c>
       <c r="H82" t="n">
-        <v>2921</v>
+        <v>2843</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.00366477925659723</v>
+        <v>-0.003297047700633083</v>
       </c>
       <c r="J82" t="n">
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83">
@@ -14963,7 +14963,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.8228689583438187</v>
+        <v>-0.8229343104865082</v>
       </c>
       <c r="J83" t="n">
         <v>8264</v>
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -14905,13 +14905,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>263111</v>
+        <v>264715</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.0003571360726429969</v>
+        <v>0.005736973081818354</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.07998525337215091</v>
+        <v>-0.08555994182422605</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -14905,13 +14905,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>264715</v>
+        <v>265167</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.005736973081818354</v>
+        <v>0.007454265686442127</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.08555994182422605</v>
+        <v>-0.08711868369744349</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83">
@@ -7587,13 +7587,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>276851</v>
+        <v>277009</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>6421</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.01115460721352697</v>
+        <v>0.01234400337174166</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.312449657035734</v>
+        <v>-0.3284091310023639</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83">
@@ -7596,7 +7596,7 @@
         <v>0.01234400337174166</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -14914,7 +14914,7 @@
         <v>0.007454265686442127</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>225954</v>
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83">
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83">
@@ -7587,13 +7587,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>277009</v>
+        <v>277801</v>
       </c>
       <c r="C82" t="n">
         <v>6421</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.01234400337174166</v>
+        <v>0.01517283747776579</v>
       </c>
       <c r="E82" t="n">
         <v>2</v>
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.3284091310023639</v>
+        <v>-0.3302805553405437</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83">
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83">
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83">
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83">
@@ -11273,7 +11273,7 @@
         <v>4100</v>
       </c>
       <c r="K82" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83">
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83">
@@ -7596,7 +7596,7 @@
         <v>0.01517283747776579</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83">
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -14914,7 +14914,7 @@
         <v>0.007454265686442127</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>225954</v>
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83">
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83">
@@ -11273,7 +11273,7 @@
         <v>4100</v>
       </c>
       <c r="K82" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83">
@@ -7596,7 +7596,7 @@
         <v>0.01517283747776579</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83">
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -14914,7 +14914,7 @@
         <v>0.007454265686442127</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>225954</v>
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83">
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83">
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83">
@@ -11273,7 +11273,7 @@
         <v>4100</v>
       </c>
       <c r="K82" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83">
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -7596,7 +7596,7 @@
         <v>0.01517283747776579</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -14914,7 +14914,7 @@
         <v>0.007454265686442127</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>225954</v>
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -3955,7 +3955,7 @@
         <v>17494</v>
       </c>
       <c r="K82" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83">
@@ -7596,7 +7596,7 @@
         <v>0.01517283747776579</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83">
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -11273,7 +11273,7 @@
         <v>4100</v>
       </c>
       <c r="K82" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83">
@@ -14914,7 +14914,7 @@
         <v>0.007454265686442127</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>225954</v>
@@ -14932,7 +14932,7 @@
         <v>28880</v>
       </c>
       <c r="K82" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83">
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7614,7 +7614,7 @@
         <v>18627</v>
       </c>
       <c r="K82" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -7596,7 +7596,7 @@
         <v>0.01517283747776579</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -14914,19 +14914,19 @@
         <v>0.007454265686442127</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>225954</v>
+        <v>226011</v>
       </c>
       <c r="G82" t="n">
         <v>9719</v>
       </c>
       <c r="H82" t="n">
-        <v>2843</v>
+        <v>3635</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.003297047700633083</v>
+        <v>0.0002507260608846451</v>
       </c>
       <c r="J82" t="n">
         <v>28880</v>
@@ -14963,7 +14963,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.8229343104865082</v>
+        <v>-0.8235623420299543</v>
       </c>
       <c r="J83" t="n">
         <v>8264</v>
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3937,7 +3937,7 @@
         <v>3.115905450964996e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>50052</v>
@@ -7596,7 +7596,7 @@
         <v>0.01517283747776579</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>243101</v>
@@ -11255,7 +11255,7 @@
         <v>0.007089484602525629</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>40620</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>18266</v>
+        <v>18334</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.5974716510227335</v>
+        <v>0.5993163691606532</v>
       </c>
       <c r="J82" t="n">
         <v>4100</v>
@@ -11304,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.3886322725265768</v>
+        <v>-0.3893374495369271</v>
       </c>
       <c r="J83" t="n">
         <v>230</v>
@@ -14905,16 +14905,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>265167</v>
+        <v>265727</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.007454265686442127</v>
+        <v>0.009581884842613173</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>226011</v>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.08711868369744349</v>
+        <v>-0.089042513557147</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -7611,10 +7611,10 @@
         <v>0.09687989801676036</v>
       </c>
       <c r="J82" t="n">
-        <v>18627</v>
+        <v>18659</v>
       </c>
       <c r="K82" t="n">
-        <v>114</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83">
@@ -14905,13 +14905,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>265727</v>
+        <v>265729</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.009581884842613173</v>
+        <v>0.00958948348245664</v>
       </c>
       <c r="E82" t="n">
         <v>10</v>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.089042513557147</v>
+        <v>-0.08904936984672354</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>

--- a/regionais/registroPNB.xlsx
+++ b/regionais/registroPNB.xlsx
@@ -3952,10 +3952,10 @@
         <v>0.008483810709838106</v>
       </c>
       <c r="J82" t="n">
-        <v>17494</v>
+        <v>17508</v>
       </c>
       <c r="K82" t="n">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83">
@@ -14905,13 +14905,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>265729</v>
+        <v>265363</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.00958948348245664</v>
+        <v>0.008198932391101994</v>
       </c>
       <c r="E82" t="n">
         <v>10</v>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.08904936984672354</v>
+        <v>-0.08779294777342735</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>
